--- a/NECP Scenario/Results/Regional Results/EL52_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL52_Capacity.xlsx
@@ -507,25 +507,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.176540412192067E-11</v>
+        <v>1.737117424794809E-11</v>
       </c>
       <c r="C2">
-        <v>6.160913831215755E-12</v>
+        <v>9.096370267531972E-12</v>
       </c>
       <c r="D2">
-        <v>9.052365852681536E-12</v>
+        <v>1.336548990486888E-11</v>
       </c>
       <c r="E2">
-        <v>1.330101165334147E-11</v>
+        <v>1.963844795922447E-11</v>
       </c>
       <c r="F2">
-        <v>1.954362089602539E-11</v>
+        <v>2.885541088104899E-11</v>
       </c>
       <c r="G2">
-        <v>2.871589208827188E-11</v>
+        <v>4.23979271163183E-11</v>
       </c>
       <c r="H2">
-        <v>1.740394568256181E-10</v>
+        <v>2.569628070818161E-10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.50188218791605E-08</v>
+        <v>3.762702410683653E-08</v>
       </c>
       <c r="C3">
-        <v>2.508687248666296E-08</v>
+        <v>3.773362570315518E-08</v>
       </c>
       <c r="D3">
-        <v>5.532767856847908E-08</v>
+        <v>8.117500105715253E-08</v>
       </c>
       <c r="E3">
-        <v>1.16708214503862E-07</v>
+        <v>1.663308236525741E-07</v>
       </c>
       <c r="F3">
-        <v>1.57383435620906E-06</v>
+        <v>1.782148648122868E-06</v>
       </c>
       <c r="G3">
-        <v>0.7616203873235962</v>
+        <v>0.6122377896885377</v>
       </c>
       <c r="H3">
-        <v>0.9118400736930669</v>
+        <v>0.8380343969148341</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,22 +562,22 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.1228211692644976</v>
+        <v>0.1229649497980376</v>
       </c>
       <c r="D4">
-        <v>0.1228211692898201</v>
+        <v>0.1229649498473863</v>
       </c>
       <c r="E4">
-        <v>0.1474197018846618</v>
+        <v>0.1476130226346497</v>
       </c>
       <c r="F4">
-        <v>0.1679892845784917</v>
+        <v>0.1692737047771477</v>
       </c>
       <c r="G4">
-        <v>0.1834274740512314</v>
+        <v>0.1840508912241918</v>
       </c>
       <c r="H4">
-        <v>0.193775820897947</v>
+        <v>0.1964784340208628</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,22 +692,22 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1.51856640162125E-08</v>
+        <v>2.284030993846557E-08</v>
       </c>
       <c r="D9">
-        <v>1.821121738213257E-08</v>
+        <v>2.804195319709356E-08</v>
       </c>
       <c r="E9">
-        <v>2.40301180876514E-08</v>
+        <v>3.627618923062965E-08</v>
       </c>
       <c r="F9">
-        <v>2.427611140150693E-08</v>
+        <v>3.651921606673262E-08</v>
       </c>
       <c r="G9">
-        <v>2.440012524399474E-08</v>
+        <v>3.669203474550008E-08</v>
       </c>
       <c r="H9">
-        <v>1.15722065464977E-07</v>
+        <v>1.755866635482169E-07</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>4.327038892002927</v>
+        <v>4.32703889200374</v>
       </c>
       <c r="C13">
-        <v>4.327038892004654</v>
+        <v>4.32703889200628</v>
       </c>
       <c r="D13">
-        <v>4.327038892007795</v>
+        <v>4.327038892011491</v>
       </c>
       <c r="E13">
-        <v>4.32703889201697</v>
+        <v>4.327038892021291</v>
       </c>
       <c r="F13">
-        <v>4.327038892036655</v>
+        <v>4.327038892037887</v>
       </c>
       <c r="G13">
-        <v>4.327038892057947</v>
+        <v>4.327038892070749</v>
       </c>
       <c r="H13">
-        <v>4.327038892302372</v>
+        <v>4.327038892371545</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -923,25 +923,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.784906631384171E-08</v>
+        <v>2.679016949950934E-08</v>
       </c>
       <c r="C18">
-        <v>1.785936363715609E-08</v>
+        <v>2.680585401049161E-08</v>
       </c>
       <c r="D18">
-        <v>3.271917660397829E-08</v>
+        <v>4.833927538069392E-08</v>
       </c>
       <c r="E18">
-        <v>7.271054719850564E-08</v>
+        <v>1.04618613646424E-07</v>
       </c>
       <c r="F18">
-        <v>4.432761731654448E-07</v>
+        <v>5.829652662435251E-07</v>
       </c>
       <c r="G18">
-        <v>1.028859886419578E-06</v>
+        <v>1.522164146530429E-06</v>
       </c>
       <c r="H18">
-        <v>1.653066266888206E-06</v>
+        <v>2.746308009789574E-06</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -952,22 +952,22 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>1.00939559536491E-08</v>
+        <v>1.553320953777433E-08</v>
       </c>
       <c r="D19">
-        <v>1.549103933159216E-08</v>
+        <v>2.389912896692285E-08</v>
       </c>
       <c r="E19">
-        <v>4.587710977781897E-08</v>
+        <v>7.466142664209567E-08</v>
       </c>
       <c r="F19">
-        <v>0.1079172228181443</v>
+        <v>0.1079172227631085</v>
       </c>
       <c r="G19">
-        <v>0.1079172229162488</v>
+        <v>0.10791722289108</v>
       </c>
       <c r="H19">
-        <v>0.1079172229602585</v>
+        <v>0.1079172229492425</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1027,25 +1027,25 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.41098094987873E-08</v>
+        <v>3.568432430037246E-08</v>
       </c>
       <c r="C22">
-        <v>2.413795853748543E-08</v>
+        <v>3.572596089607717E-08</v>
       </c>
       <c r="D22">
-        <v>2.711606414511386E-08</v>
+        <v>4.014907844772655E-08</v>
       </c>
       <c r="E22">
-        <v>3.962616249111668E-08</v>
+        <v>5.868847447110397E-08</v>
       </c>
       <c r="F22">
-        <v>5.820970913892934E-08</v>
+        <v>8.602351906108405E-08</v>
       </c>
       <c r="G22">
-        <v>8.470754300486016E-08</v>
+        <v>1.254507867302033E-07</v>
       </c>
       <c r="H22">
-        <v>5.084072119057743E-07</v>
+        <v>7.561265378503926E-07</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>5.665857847540953E-09</v>
+        <v>8.379663607877802E-09</v>
       </c>
       <c r="D24">
-        <v>2.4111843432293E-08</v>
+        <v>3.672479282384624E-08</v>
       </c>
       <c r="E24">
-        <v>1.884401712978713E-07</v>
+        <v>3.04119283518765E-07</v>
       </c>
       <c r="F24">
-        <v>1.138208366016224</v>
+        <v>0.9211420474822464</v>
       </c>
       <c r="G24">
-        <v>2.691633912261325</v>
+        <v>2.773347388422359</v>
       </c>
       <c r="H24">
-        <v>4.069305551251232</v>
+        <v>4.370685921355197</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1160,22 +1160,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>2.712323676589844E-07</v>
+        <v>1.193327895081014E-07</v>
       </c>
       <c r="D27">
-        <v>0.2652368877568472</v>
+        <v>0.1728875518745642</v>
       </c>
       <c r="E27">
-        <v>0.7069894372641068</v>
+        <v>0.5139441268190201</v>
       </c>
       <c r="F27">
-        <v>1.634977049358521</v>
+        <v>1.216749314009557</v>
       </c>
       <c r="G27">
-        <v>3.340787261074385</v>
+        <v>2.797914118725171</v>
       </c>
       <c r="H27">
-        <v>4.223682874868381</v>
+        <v>3.918351071281994</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1212,22 +1212,22 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>7.821955940736383E-09</v>
+        <v>1.168305228301508E-08</v>
       </c>
       <c r="D29">
-        <v>2.65819642218654E-08</v>
+        <v>4.205575197965137E-08</v>
       </c>
       <c r="E29">
-        <v>1.009020799453815E-07</v>
+        <v>2.033884068179717E-07</v>
       </c>
       <c r="F29">
-        <v>2.001886585617781</v>
+        <v>2.001886588620887</v>
       </c>
       <c r="G29">
-        <v>2.001886590430283</v>
+        <v>2.001886590412057</v>
       </c>
       <c r="H29">
-        <v>2.00188659076356</v>
+        <v>2.001886590751476</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1264,22 +1264,22 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>6.746423269326583E-09</v>
+        <v>1.004786436505416E-08</v>
       </c>
       <c r="D31">
-        <v>8.672557651004702E-09</v>
+        <v>1.307212330157122E-08</v>
       </c>
       <c r="E31">
-        <v>1.61456825981397E-08</v>
+        <v>2.438615393490764E-08</v>
       </c>
       <c r="F31">
-        <v>2.77012192989047E-08</v>
+        <v>4.132747566659492E-08</v>
       </c>
       <c r="G31">
-        <v>3.837760003462585E-08</v>
+        <v>5.801958354745344E-08</v>
       </c>
       <c r="H31">
-        <v>2.000051735902353E-07</v>
+        <v>3.084200482762062E-07</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1316,22 +1316,22 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>2.20281434908889E-07</v>
+        <v>3.550563830205831E-07</v>
       </c>
       <c r="D33">
-        <v>2.204829476284408E-07</v>
+        <v>3.554629063538222E-07</v>
       </c>
       <c r="E33">
-        <v>0.7222926818726454</v>
+        <v>0.600868861265951</v>
       </c>
       <c r="F33">
-        <v>0.7222926819882628</v>
+        <v>0.6008688614049071</v>
       </c>
       <c r="G33">
-        <v>0.7222926820969763</v>
+        <v>0.600868861543813</v>
       </c>
       <c r="H33">
-        <v>0.7222926828002093</v>
+        <v>0.6008688623794102</v>
       </c>
     </row>
     <row r="34" spans="1:8">
